--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/100.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/100.xlsx
@@ -426,13 +426,13 @@
         <v>-15.86408332317394</v>
       </c>
       <c r="E2">
-        <v>-7.363767246002393</v>
+        <v>-7.325039736288796</v>
       </c>
       <c r="F2">
-        <v>-4.151746092117324</v>
+        <v>-4.218595341523244</v>
       </c>
       <c r="G2">
-        <v>-4.155520401746481</v>
+        <v>-4.662053732528208</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-15.57927276208503</v>
       </c>
       <c r="E3">
-        <v>-8.218263120405744</v>
+        <v>-8.783715555847511</v>
       </c>
       <c r="F3">
-        <v>-4.12982500553704</v>
+        <v>-4.534111373208145</v>
       </c>
       <c r="G3">
-        <v>-3.621685001902384</v>
+        <v>-4.257978475641385</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-15.37265777663902</v>
       </c>
       <c r="E4">
-        <v>-9.350191426415011</v>
+        <v>-9.496107915890166</v>
       </c>
       <c r="F4">
-        <v>-4.2072790144336</v>
+        <v>-4.394705422991016</v>
       </c>
       <c r="G4">
-        <v>-3.616699320320242</v>
+        <v>-3.461421492346266</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-15.28399653360453</v>
       </c>
       <c r="E5">
-        <v>-9.521757192669609</v>
+        <v>-9.750734952393454</v>
       </c>
       <c r="F5">
-        <v>-4.050899816133109</v>
+        <v>-4.173843620954403</v>
       </c>
       <c r="G5">
-        <v>-4.323994064239992</v>
+        <v>-4.103041633857954</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.29556808977648</v>
       </c>
       <c r="E6">
-        <v>-9.605330180481166</v>
+        <v>-9.880507432031264</v>
       </c>
       <c r="F6">
-        <v>-3.944130713218878</v>
+        <v>-4.450757731668847</v>
       </c>
       <c r="G6">
-        <v>-3.491226333836325</v>
+        <v>-3.819612588058791</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.39862160073695</v>
       </c>
       <c r="E7">
-        <v>-11.32789829436286</v>
+        <v>-12.20965105381838</v>
       </c>
       <c r="F7">
-        <v>-4.124028918819652</v>
+        <v>-3.989038166859445</v>
       </c>
       <c r="G7">
-        <v>-3.595687287782487</v>
+        <v>-4.398630313422861</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.57309242863523</v>
       </c>
       <c r="E8">
-        <v>-12.58838544897588</v>
+        <v>-12.16589693795627</v>
       </c>
       <c r="F8">
-        <v>-3.538792318946218</v>
+        <v>-4.05115163982356</v>
       </c>
       <c r="G8">
-        <v>-3.756742017722492</v>
+        <v>-4.141440651567961</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.78866497399425</v>
       </c>
       <c r="E9">
-        <v>-13.05077434447708</v>
+        <v>-12.20514069370674</v>
       </c>
       <c r="F9">
-        <v>-4.151128958402238</v>
+        <v>-4.188066689260471</v>
       </c>
       <c r="G9">
-        <v>-4.013680078116407</v>
+        <v>-4.097225005345455</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.02381304952823</v>
       </c>
       <c r="E10">
-        <v>-14.00414944883791</v>
+        <v>-12.90012559966391</v>
       </c>
       <c r="F10">
-        <v>-3.694355575354951</v>
+        <v>-3.834102812942033</v>
       </c>
       <c r="G10">
-        <v>-3.211035001574568</v>
+        <v>-4.416808518978999</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.24221527676866</v>
       </c>
       <c r="E11">
-        <v>-14.19452649612038</v>
+        <v>-14.51623381809929</v>
       </c>
       <c r="F11">
-        <v>-3.319004081063634</v>
+        <v>-3.449983049692083</v>
       </c>
       <c r="G11">
-        <v>-3.453294103047355</v>
+        <v>-3.890699932423561</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.42183988262789</v>
       </c>
       <c r="E12">
-        <v>-15.40734240485465</v>
+        <v>-15.29984096038656</v>
       </c>
       <c r="F12">
-        <v>-3.439106585693326</v>
+        <v>-3.688479136999492</v>
       </c>
       <c r="G12">
-        <v>-3.380988477924133</v>
+        <v>-3.562075318922267</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.53320603354934</v>
       </c>
       <c r="E13">
-        <v>-16.66414338162543</v>
+        <v>-15.8727155647269</v>
       </c>
       <c r="F13">
-        <v>-3.003889807569091</v>
+        <v>-3.351916774711664</v>
       </c>
       <c r="G13">
-        <v>-3.219529861428338</v>
+        <v>-4.105938361204816</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-16.56893392273329</v>
       </c>
       <c r="E14">
-        <v>-18.26939231939041</v>
+        <v>-16.01330656876904</v>
       </c>
       <c r="F14">
-        <v>-2.939779969164229</v>
+        <v>-3.101541070480708</v>
       </c>
       <c r="G14">
-        <v>-3.879470561954353</v>
+        <v>-3.4650829557127</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-16.52670032780039</v>
       </c>
       <c r="E15">
-        <v>-18.12827148388938</v>
+        <v>-17.15106302082618</v>
       </c>
       <c r="F15">
-        <v>-2.443471923450933</v>
+        <v>-2.642696768926422</v>
       </c>
       <c r="G15">
-        <v>-2.922064102542665</v>
+        <v>-3.100035720188345</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-16.41224510408107</v>
       </c>
       <c r="E16">
-        <v>-19.33412712807386</v>
+        <v>-18.77229747183823</v>
       </c>
       <c r="F16">
-        <v>-2.156142749381091</v>
+        <v>-2.410793657777895</v>
       </c>
       <c r="G16">
-        <v>-3.413812536946007</v>
+        <v>-3.322573901883693</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-16.24983814665324</v>
       </c>
       <c r="E17">
-        <v>-19.03366740613894</v>
+        <v>-19.15652490596704</v>
       </c>
       <c r="F17">
-        <v>-1.829968114324368</v>
+        <v>-2.222124698116279</v>
       </c>
       <c r="G17">
-        <v>-2.780505175283429</v>
+        <v>-3.599279229692597</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-16.05451263546424</v>
       </c>
       <c r="E18">
-        <v>-20.6785767192631</v>
+        <v>-20.6894993985696</v>
       </c>
       <c r="F18">
-        <v>-1.142599612257575</v>
+        <v>-1.768985362865074</v>
       </c>
       <c r="G18">
-        <v>-2.885267388873666</v>
+        <v>-3.246990836676593</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-15.8526018886221</v>
       </c>
       <c r="E19">
-        <v>-21.74371456213324</v>
+        <v>-21.3248126025277</v>
       </c>
       <c r="F19">
-        <v>-0.919496248028987</v>
+        <v>-1.410602146452702</v>
       </c>
       <c r="G19">
-        <v>-3.265102831321945</v>
+        <v>-2.825449141524575</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-15.65287340518158</v>
       </c>
       <c r="E20">
-        <v>-23.38046809356958</v>
+        <v>-22.09846163047211</v>
       </c>
       <c r="F20">
-        <v>-0.4569160094880759</v>
+        <v>-0.7460187181673117</v>
       </c>
       <c r="G20">
-        <v>-3.458127499534691</v>
+        <v>-2.8856580332473</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-15.47234690048129</v>
       </c>
       <c r="E21">
-        <v>-23.51898958499021</v>
+        <v>-22.49863382158193</v>
       </c>
       <c r="F21">
-        <v>-0.3167844094260947</v>
+        <v>-0.2524890167230054</v>
       </c>
       <c r="G21">
-        <v>-2.916184573664919</v>
+        <v>-3.37691650691083</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-15.31236627909359</v>
       </c>
       <c r="E22">
-        <v>-24.40805582996812</v>
+        <v>-23.23684301194231</v>
       </c>
       <c r="F22">
-        <v>0.4740852861508857</v>
+        <v>-0.2027646066351595</v>
       </c>
       <c r="G22">
-        <v>-2.863758774505021</v>
+        <v>-3.835304573914936</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-15.17574381547093</v>
       </c>
       <c r="E23">
-        <v>-24.35283108944457</v>
+        <v>-23.28964049039774</v>
       </c>
       <c r="F23">
-        <v>0.4306100797497592</v>
+        <v>0.01383441674664679</v>
       </c>
       <c r="G23">
-        <v>-2.708500809804281</v>
+        <v>-3.099476237992208</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-15.06427700405002</v>
       </c>
       <c r="E24">
-        <v>-24.90211234420495</v>
+        <v>-24.44476364027429</v>
       </c>
       <c r="F24">
-        <v>0.5556761618570258</v>
+        <v>0.3805758602532663</v>
       </c>
       <c r="G24">
-        <v>-3.679444089926049</v>
+        <v>-4.10282975894344</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-14.97031571473799</v>
       </c>
       <c r="E25">
-        <v>-25.55189402261756</v>
+        <v>-24.95615515301249</v>
       </c>
       <c r="F25">
-        <v>0.7522709408286269</v>
+        <v>0.6662035676777582</v>
       </c>
       <c r="G25">
-        <v>-3.52853949260945</v>
+        <v>-4.252403516953252</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-14.8956730390286</v>
       </c>
       <c r="E26">
-        <v>-25.13294224979793</v>
+        <v>-23.92278002683215</v>
       </c>
       <c r="F26">
-        <v>1.01570668553212</v>
+        <v>0.7693286823870743</v>
       </c>
       <c r="G26">
-        <v>-3.359810918109416</v>
+        <v>-4.316498989139082</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-14.82759384476492</v>
       </c>
       <c r="E27">
-        <v>-25.68222803303232</v>
+        <v>-24.6326273844825</v>
       </c>
       <c r="F27">
-        <v>1.043178662078563</v>
+        <v>0.9940664155013857</v>
       </c>
       <c r="G27">
-        <v>-4.292262485246077</v>
+        <v>-3.794694111784696</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-14.76555407123279</v>
       </c>
       <c r="E28">
-        <v>-25.15326604114436</v>
+        <v>-23.47998583836214</v>
       </c>
       <c r="F28">
-        <v>1.004336514561294</v>
+        <v>0.787009356232427</v>
       </c>
       <c r="G28">
-        <v>-4.500419657118831</v>
+        <v>-4.481513131544054</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-14.69402816640861</v>
       </c>
       <c r="E29">
-        <v>-25.46518280231868</v>
+        <v>-24.2755028672896</v>
       </c>
       <c r="F29">
-        <v>0.92666215993559</v>
+        <v>0.8148242768836288</v>
       </c>
       <c r="G29">
-        <v>-3.969371736618801</v>
+        <v>-4.51532704368217</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-14.61358372464001</v>
       </c>
       <c r="E30">
-        <v>-25.46981543122853</v>
+        <v>-24.15610512160336</v>
       </c>
       <c r="F30">
-        <v>1.114976578348807</v>
+        <v>0.5222382832756209</v>
       </c>
       <c r="G30">
-        <v>-4.151140549998025</v>
+        <v>-4.097082651887266</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-14.520242864896</v>
       </c>
       <c r="E31">
-        <v>-24.72386255031503</v>
+        <v>-23.82945270600807</v>
       </c>
       <c r="F31">
-        <v>1.221539417779741</v>
+        <v>1.122856009084236</v>
       </c>
       <c r="G31">
-        <v>-4.356904197445886</v>
+        <v>-4.116922751304118</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-14.40804452014101</v>
       </c>
       <c r="E32">
-        <v>-24.36622631555926</v>
+        <v>-22.43513103057236</v>
       </c>
       <c r="F32">
-        <v>0.7205477827710171</v>
+        <v>0.9500453149818144</v>
       </c>
       <c r="G32">
-        <v>-4.140599773000986</v>
+        <v>-4.90392881071844</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-14.28271158843204</v>
       </c>
       <c r="E33">
-        <v>-24.16188345443715</v>
+        <v>-23.0115469015867</v>
       </c>
       <c r="F33">
-        <v>0.6323879535606768</v>
+        <v>0.5229316267917642</v>
       </c>
       <c r="G33">
-        <v>-3.919200418971147</v>
+        <v>-4.772387594261038</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-14.14018824046748</v>
       </c>
       <c r="E34">
-        <v>-23.90247434938176</v>
+        <v>-22.91638554878951</v>
       </c>
       <c r="F34">
-        <v>0.6375395704386869</v>
+        <v>0.4208403146011419</v>
       </c>
       <c r="G34">
-        <v>-4.247517151737288</v>
+        <v>-4.542890645842141</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-13.98917284405962</v>
       </c>
       <c r="E35">
-        <v>-22.91256804520105</v>
+        <v>-22.14212970532807</v>
       </c>
       <c r="F35">
-        <v>0.736343092407598</v>
+        <v>0.414357511306833</v>
       </c>
       <c r="G35">
-        <v>-3.460064168675165</v>
+        <v>-4.12209382343646</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-13.82402504259634</v>
       </c>
       <c r="E36">
-        <v>-22.81224423203512</v>
+        <v>-22.10683477891229</v>
       </c>
       <c r="F36">
-        <v>0.2463438928340232</v>
+        <v>0.4278723254835069</v>
       </c>
       <c r="G36">
-        <v>-3.115532383857673</v>
+        <v>-4.28484355269257</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-13.65372467381012</v>
       </c>
       <c r="E37">
-        <v>-21.35430202526565</v>
+        <v>-21.85977935094983</v>
       </c>
       <c r="F37">
-        <v>0.244089076763603</v>
+        <v>0.2608850542227658</v>
       </c>
       <c r="G37">
-        <v>-2.766534673107705</v>
+        <v>-4.661077121594123</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-13.47593099061514</v>
       </c>
       <c r="E38">
-        <v>-22.11475507995171</v>
+        <v>-21.03814661242014</v>
       </c>
       <c r="F38">
-        <v>0.2323685063813928</v>
+        <v>0.02460484971784596</v>
       </c>
       <c r="G38">
-        <v>-3.730158337042144</v>
+        <v>-4.158880605468841</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-13.29181189099209</v>
       </c>
       <c r="E39">
-        <v>-21.14750925970538</v>
+        <v>-20.74866843995382</v>
       </c>
       <c r="F39">
-        <v>-0.09662671968186168</v>
+        <v>-0.02999118906586385</v>
       </c>
       <c r="G39">
-        <v>-2.281331187235502</v>
+        <v>-3.392376754579226</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-13.10270212048991</v>
       </c>
       <c r="E40">
-        <v>-19.7413410962656</v>
+        <v>-19.00392438885656</v>
       </c>
       <c r="F40">
-        <v>0.1373158320123579</v>
+        <v>0.1478112470058276</v>
       </c>
       <c r="G40">
-        <v>-3.022870214213472</v>
+        <v>-3.801712468327951</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-12.9022020849885</v>
       </c>
       <c r="E41">
-        <v>-19.63015347395527</v>
+        <v>-19.63672881821441</v>
       </c>
       <c r="F41">
-        <v>-0.1505807737284019</v>
+        <v>-0.1827504218161207</v>
       </c>
       <c r="G41">
-        <v>-2.80398687479348</v>
+        <v>-3.700231005367133</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-12.69013664829641</v>
       </c>
       <c r="E42">
-        <v>-18.56789121208001</v>
+        <v>-19.49978323574845</v>
       </c>
       <c r="F42">
-        <v>-0.7336014907993471</v>
+        <v>-0.6077227802699342</v>
       </c>
       <c r="G42">
-        <v>-2.205168776559029</v>
+        <v>-3.683022789654001</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-12.45481696134542</v>
       </c>
       <c r="E43">
-        <v>-18.66926563121572</v>
+        <v>-18.77713841055243</v>
       </c>
       <c r="F43">
-        <v>-0.4182900658629377</v>
+        <v>-0.373948387158483</v>
       </c>
       <c r="G43">
-        <v>-2.227915534959361</v>
+        <v>-3.039836760102237</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-12.19852578281257</v>
       </c>
       <c r="E44">
-        <v>-18.25582048278942</v>
+        <v>-17.46859508977001</v>
       </c>
       <c r="F44">
-        <v>-0.7666243573119494</v>
+        <v>-0.6469741412841861</v>
       </c>
       <c r="G44">
-        <v>-1.751753148954908</v>
+        <v>-2.803049990405866</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.91134058414972</v>
       </c>
       <c r="E45">
-        <v>-16.72403245037687</v>
+        <v>-16.9528834128285</v>
       </c>
       <c r="F45">
-        <v>-0.7814620742308942</v>
+        <v>-0.5760195030299916</v>
       </c>
       <c r="G45">
-        <v>-2.069085491621747</v>
+        <v>-2.244057755008847</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.59744330907067</v>
       </c>
       <c r="E46">
-        <v>-17.23184646864901</v>
+        <v>-15.71485748929352</v>
       </c>
       <c r="F46">
-        <v>-0.790725706896401</v>
+        <v>-0.7611032885722907</v>
       </c>
       <c r="G46">
-        <v>-2.044163704802114</v>
+        <v>-2.817010560944972</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.25460423479911</v>
       </c>
       <c r="E47">
-        <v>-15.94627156803349</v>
+        <v>-16.0880852600577</v>
       </c>
       <c r="F47">
-        <v>-0.9020864503243498</v>
+        <v>-0.7772150345567411</v>
       </c>
       <c r="G47">
-        <v>-1.774979936458434</v>
+        <v>-2.016249184814979</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.88339669328181</v>
       </c>
       <c r="E48">
-        <v>-15.50896136158677</v>
+        <v>-15.35530571003251</v>
       </c>
       <c r="F48">
-        <v>-0.9664083507843286</v>
+        <v>-0.9421628652717898</v>
       </c>
       <c r="G48">
-        <v>-1.368312522414362</v>
+        <v>-2.85649543759186</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.48793885752695</v>
       </c>
       <c r="E49">
-        <v>-14.74362208344644</v>
+        <v>-14.81821510730078</v>
       </c>
       <c r="F49">
-        <v>-1.215664930654103</v>
+        <v>-1.108754176913993</v>
       </c>
       <c r="G49">
-        <v>-1.975426847770226</v>
+        <v>-2.228743171344179</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.06649685893766</v>
       </c>
       <c r="E50">
-        <v>-14.57722330603459</v>
+        <v>-14.47951242237109</v>
       </c>
       <c r="F50">
-        <v>-1.275906293287891</v>
+        <v>-1.430694197807604</v>
       </c>
       <c r="G50">
-        <v>-1.866112634063491</v>
+        <v>-1.950511682041671</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.631035175033785</v>
       </c>
       <c r="E51">
-        <v>-15.00190359847392</v>
+        <v>-13.86912393935121</v>
       </c>
       <c r="F51">
-        <v>-1.301849931976169</v>
+        <v>-1.544129173212162</v>
       </c>
       <c r="G51">
-        <v>-1.633066780826496</v>
+        <v>-2.92154103634746</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.180145519965818</v>
       </c>
       <c r="E52">
-        <v>-13.76250101884061</v>
+        <v>-13.79127041421134</v>
       </c>
       <c r="F52">
-        <v>-1.369439741840192</v>
+        <v>-1.350657339349116</v>
       </c>
       <c r="G52">
-        <v>-1.987298464074053</v>
+        <v>-2.805880506841943</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.729760576864271</v>
       </c>
       <c r="E53">
-        <v>-13.20176272484083</v>
+        <v>-13.84830654433795</v>
       </c>
       <c r="F53">
-        <v>-1.48416779876052</v>
+        <v>-1.633770123338708</v>
       </c>
       <c r="G53">
-        <v>-1.950842736595598</v>
+        <v>-2.447057096931417</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.284676241037676</v>
       </c>
       <c r="E54">
-        <v>-12.33296592952125</v>
+        <v>-12.54657404846306</v>
       </c>
       <c r="F54">
-        <v>-1.566847149233939</v>
+        <v>-1.471931155486366</v>
       </c>
       <c r="G54">
-        <v>-2.214895159353408</v>
+        <v>-2.117575052135452</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.855081996768828</v>
       </c>
       <c r="E55">
-        <v>-11.67846558119266</v>
+        <v>-12.01658409297536</v>
       </c>
       <c r="F55">
-        <v>-1.428890013604307</v>
+        <v>-1.279691932318685</v>
       </c>
       <c r="G55">
-        <v>-1.305974949909885</v>
+        <v>-2.182716656711691</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.448954619074261</v>
       </c>
       <c r="E56">
-        <v>-11.36017725708954</v>
+        <v>-11.83540890487649</v>
       </c>
       <c r="F56">
-        <v>-1.49536152747455</v>
+        <v>-1.361950472151481</v>
       </c>
       <c r="G56">
-        <v>-1.836109159841077</v>
+        <v>-1.992145102743546</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.07038212666936</v>
       </c>
       <c r="E57">
-        <v>-11.766046268501</v>
+        <v>-11.66379785388181</v>
       </c>
       <c r="F57">
-        <v>-1.547397082616207</v>
+        <v>-1.843226134606174</v>
       </c>
       <c r="G57">
-        <v>-1.853466350103476</v>
+        <v>-2.501793656877727</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.72627695731731</v>
       </c>
       <c r="E58">
-        <v>-10.26194532617134</v>
+        <v>-11.33020781610677</v>
       </c>
       <c r="F58">
-        <v>-1.510186818882453</v>
+        <v>-1.734442442168335</v>
       </c>
       <c r="G58">
-        <v>-1.999547482569356</v>
+        <v>-2.707570546507745</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.411631661111573</v>
       </c>
       <c r="E59">
-        <v>-11.0626610432596</v>
+        <v>-11.01898843992963</v>
       </c>
       <c r="F59">
-        <v>-1.356232251969956</v>
+        <v>-1.562412898526753</v>
       </c>
       <c r="G59">
-        <v>-2.814504477971744</v>
+        <v>-2.965958625847862</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.131796486120887</v>
       </c>
       <c r="E60">
-        <v>-8.860541117387639</v>
+        <v>-10.36103739440719</v>
       </c>
       <c r="F60">
-        <v>-1.45717296183809</v>
+        <v>-1.240758664387108</v>
       </c>
       <c r="G60">
-        <v>-1.848344936154223</v>
+        <v>-2.469906482243467</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.87791377787151</v>
       </c>
       <c r="E61">
-        <v>-10.36839163619564</v>
+        <v>-9.989122881105237</v>
       </c>
       <c r="F61">
-        <v>-1.593555371035001</v>
+        <v>-1.519691506462174</v>
       </c>
       <c r="G61">
-        <v>-2.980521715675116</v>
+        <v>-2.937233022203606</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.650890788138794</v>
       </c>
       <c r="E62">
-        <v>-8.443667914137535</v>
+        <v>-8.913895598146011</v>
       </c>
       <c r="F62">
-        <v>-1.586511763008996</v>
+        <v>-1.705992163719186</v>
       </c>
       <c r="G62">
-        <v>-2.964485433082886</v>
+        <v>-2.477673022078597</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.446047063912829</v>
       </c>
       <c r="E63">
-        <v>-9.08310655791662</v>
+        <v>-9.59012356476341</v>
       </c>
       <c r="F63">
-        <v>-2.042375598648009</v>
+        <v>-1.996025128991766</v>
       </c>
       <c r="G63">
-        <v>-3.559764558135856</v>
+        <v>-2.698165286630676</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.259431295525722</v>
       </c>
       <c r="E64">
-        <v>-8.905151114837199</v>
+        <v>-9.100160791029507</v>
       </c>
       <c r="F64">
-        <v>-1.866062567166551</v>
+        <v>-1.693112707340459</v>
       </c>
       <c r="G64">
-        <v>-3.038932981170016</v>
+        <v>-2.966448586587674</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.089533694158998</v>
       </c>
       <c r="E65">
-        <v>-7.909507234088771</v>
+        <v>-9.322825857986659</v>
       </c>
       <c r="F65">
-        <v>-1.415462178004927</v>
+        <v>-1.745468840666999</v>
       </c>
       <c r="G65">
-        <v>-3.486637917718895</v>
+        <v>-3.597998048568899</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.930602522834332</v>
       </c>
       <c r="E66">
-        <v>-8.580627082025519</v>
+        <v>-9.066401017302326</v>
       </c>
       <c r="F66">
-        <v>-1.845156230654697</v>
+        <v>-2.183125160792479</v>
       </c>
       <c r="G66">
-        <v>-3.596541408531619</v>
+        <v>-3.821006327730824</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.784780246787539</v>
       </c>
       <c r="E67">
-        <v>-8.846697572346191</v>
+        <v>-8.299499415629342</v>
       </c>
       <c r="F67">
-        <v>-2.09759622645343</v>
+        <v>-2.168579857566722</v>
       </c>
       <c r="G67">
-        <v>-3.454684532173849</v>
+        <v>-3.517661039967405</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.647702303470165</v>
       </c>
       <c r="E68">
-        <v>-8.106681520856746</v>
+        <v>-8.40273956605621</v>
       </c>
       <c r="F68">
-        <v>-2.442852304633639</v>
+        <v>-1.864023126620859</v>
       </c>
       <c r="G68">
-        <v>-4.198206575929843</v>
+        <v>-4.35834428475547</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.523171904698938</v>
       </c>
       <c r="E69">
-        <v>-7.869946485157763</v>
+        <v>-8.112428154372481</v>
       </c>
       <c r="F69">
-        <v>-2.326205748808426</v>
+        <v>-2.222146235668752</v>
       </c>
       <c r="G69">
-        <v>-3.809058568879594</v>
+        <v>-3.593535433181961</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.411988795323253</v>
       </c>
       <c r="E70">
-        <v>-8.041068460959611</v>
+        <v>-8.916399844272252</v>
       </c>
       <c r="F70">
-        <v>-1.993265837173041</v>
+        <v>-2.10601740947029</v>
       </c>
       <c r="G70">
-        <v>-3.59231384187797</v>
+        <v>-3.477351837481239</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.315927891227124</v>
       </c>
       <c r="E71">
-        <v>-7.69829014942301</v>
+        <v>-8.049002347421048</v>
       </c>
       <c r="F71">
-        <v>-2.36965361908526</v>
+        <v>-2.255686831808104</v>
       </c>
       <c r="G71">
-        <v>-3.719932061871335</v>
+        <v>-3.556963836609632</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.238703045383162</v>
       </c>
       <c r="E72">
-        <v>-7.819512870134338</v>
+        <v>-7.395543548114216</v>
       </c>
       <c r="F72">
-        <v>-2.401717236145421</v>
+        <v>-2.34520352682423</v>
       </c>
       <c r="G72">
-        <v>-3.577535566590664</v>
+        <v>-3.268194880855625</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.179695626235072</v>
       </c>
       <c r="E73">
-        <v>-7.833071121313303</v>
+        <v>-8.271662885904192</v>
       </c>
       <c r="F73">
-        <v>-2.504892052898905</v>
+        <v>-2.402278869244519</v>
       </c>
       <c r="G73">
-        <v>-3.687008686483283</v>
+        <v>-2.504455335491301</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.140928523992006</v>
       </c>
       <c r="E74">
-        <v>-8.132865157569096</v>
+        <v>-8.57343133682733</v>
       </c>
       <c r="F74">
-        <v>-2.564010149334497</v>
+        <v>-2.608246625378796</v>
       </c>
       <c r="G74">
-        <v>-2.944969767128882</v>
+        <v>-3.18990709994294</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.11721309733816</v>
       </c>
       <c r="E75">
-        <v>-8.771905295635506</v>
+        <v>-8.268080862964124</v>
       </c>
       <c r="F75">
-        <v>-2.748893469965319</v>
+        <v>-2.490219181093117</v>
       </c>
       <c r="G75">
-        <v>-2.891477972305339</v>
+        <v>-2.527827786998555</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.107067036117297</v>
       </c>
       <c r="E76">
-        <v>-8.841064150680648</v>
+        <v>-9.25438250183473</v>
       </c>
       <c r="F76">
-        <v>-2.869244484815851</v>
+        <v>-2.63597042561569</v>
       </c>
       <c r="G76">
-        <v>-2.487455684147144</v>
+        <v>-2.104395770343614</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.103734042364694</v>
       </c>
       <c r="E77">
-        <v>-9.531561338896216</v>
+        <v>-9.447680414852138</v>
       </c>
       <c r="F77">
-        <v>-2.764355775905974</v>
+        <v>-2.743544701645442</v>
       </c>
       <c r="G77">
-        <v>-1.687320001124073</v>
+        <v>-2.220549571134482</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.100976693126837</v>
       </c>
       <c r="E78">
-        <v>-8.977642926751987</v>
+        <v>-9.238247548945399</v>
       </c>
       <c r="F78">
-        <v>-2.985830569820659</v>
+        <v>-3.203261274074876</v>
       </c>
       <c r="G78">
-        <v>-1.897725033417992</v>
+        <v>-1.877418147080103</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.094375138115336</v>
       </c>
       <c r="E79">
-        <v>-9.956585795360125</v>
+        <v>-10.20899840807366</v>
       </c>
       <c r="F79">
-        <v>-2.852119645497776</v>
+        <v>-3.006347573653197</v>
       </c>
       <c r="G79">
-        <v>-1.698258043585825</v>
+        <v>-2.310139554518239</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.078267185759244</v>
       </c>
       <c r="E80">
-        <v>-9.717686149085475</v>
+        <v>-10.75393232778668</v>
       </c>
       <c r="F80">
-        <v>-3.122200553506527</v>
+        <v>-3.251380308136096</v>
       </c>
       <c r="G80">
-        <v>-1.443329484334247</v>
+        <v>-1.531260884402829</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.052022506883959</v>
       </c>
       <c r="E81">
-        <v>-11.92987287267649</v>
+        <v>-11.28849151354811</v>
       </c>
       <c r="F81">
-        <v>-3.051691576915039</v>
+        <v>-3.087608759133023</v>
       </c>
       <c r="G81">
-        <v>-0.7838191547283373</v>
+        <v>-1.125808440571669</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.01541440743391</v>
       </c>
       <c r="E82">
-        <v>-12.51659102205828</v>
+        <v>-12.09065634231883</v>
       </c>
       <c r="F82">
-        <v>-3.16159439371406</v>
+        <v>-3.060372038928975</v>
       </c>
       <c r="G82">
-        <v>-0.8893990730667739</v>
+        <v>-1.333667663345889</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.974555927128955</v>
       </c>
       <c r="E83">
-        <v>-12.32080244833665</v>
+        <v>-13.21686971413041</v>
       </c>
       <c r="F83">
-        <v>-3.499371142614392</v>
+        <v>-3.277642868274452</v>
       </c>
       <c r="G83">
-        <v>-0.7400669848813293</v>
+        <v>-0.4772361534275111</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.934776787644521</v>
       </c>
       <c r="E84">
-        <v>-14.44913994720164</v>
+        <v>-14.86304247150271</v>
       </c>
       <c r="F84">
-        <v>-3.401393502946072</v>
+        <v>-3.591246199626288</v>
       </c>
       <c r="G84">
-        <v>0.2810244390693186</v>
+        <v>-0.02805802411365722</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.903886637625073</v>
       </c>
       <c r="E85">
-        <v>-14.20934366307347</v>
+        <v>-14.7650327085547</v>
       </c>
       <c r="F85">
-        <v>-3.765603455669737</v>
+        <v>-3.50936291022696</v>
       </c>
       <c r="G85">
-        <v>-0.1691932015438665</v>
+        <v>-0.2700886979442345</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.893942059110047</v>
       </c>
       <c r="E86">
-        <v>-16.02744446462098</v>
+        <v>-16.34843628770668</v>
       </c>
       <c r="F86">
-        <v>-3.94796025572202</v>
+        <v>-3.838300978939421</v>
       </c>
       <c r="G86">
-        <v>0.3842869755302655</v>
+        <v>0.576563460451136</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.912160035955663</v>
       </c>
       <c r="E87">
-        <v>-17.05118752658701</v>
+        <v>-17.29131891779174</v>
       </c>
       <c r="F87">
-        <v>-4.090318507362726</v>
+        <v>-4.063977252321105</v>
       </c>
       <c r="G87">
-        <v>0.5697801526411693</v>
+        <v>0.2906912320439905</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.972911736460152</v>
       </c>
       <c r="E88">
-        <v>-17.95622117091596</v>
+        <v>-18.61775876785248</v>
       </c>
       <c r="F88">
-        <v>-4.187174537567656</v>
+        <v>-4.195305791993536</v>
       </c>
       <c r="G88">
-        <v>0.4851030188376909</v>
+        <v>0.7817278991563893</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.084661577062246</v>
       </c>
       <c r="E89">
-        <v>-18.87845848800005</v>
+        <v>-19.69457554518839</v>
       </c>
       <c r="F89">
-        <v>-4.414408141666602</v>
+        <v>-4.090814699437003</v>
       </c>
       <c r="G89">
-        <v>0.9356351612771068</v>
+        <v>0.3925600288329042</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.259388784724683</v>
       </c>
       <c r="E90">
-        <v>-21.58976908824248</v>
+        <v>-21.09028746214446</v>
       </c>
       <c r="F90">
-        <v>-4.532205299814303</v>
+        <v>-4.304600587118903</v>
       </c>
       <c r="G90">
-        <v>0.5611826658756821</v>
+        <v>0.6243578064015941</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.507664975989841</v>
       </c>
       <c r="E91">
-        <v>-22.99766260027918</v>
+        <v>-23.44120851543446</v>
       </c>
       <c r="F91">
-        <v>-4.581573511918945</v>
+        <v>-4.807854493504672</v>
       </c>
       <c r="G91">
-        <v>0.6863676348976827</v>
+        <v>0.2221430761078413</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.835370869454863</v>
       </c>
       <c r="E92">
-        <v>-25.11217466799875</v>
+        <v>-24.49966233066928</v>
       </c>
       <c r="F92">
-        <v>-4.950460426998815</v>
+        <v>-5.02791609263018</v>
       </c>
       <c r="G92">
-        <v>1.017041476087785</v>
+        <v>0.6216729539692453</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.255146432633471</v>
       </c>
       <c r="E93">
-        <v>-27.41701849826071</v>
+        <v>-27.22398323673575</v>
       </c>
       <c r="F93">
-        <v>-4.812519030349836</v>
+        <v>-5.075344268277466</v>
       </c>
       <c r="G93">
-        <v>0.2605950625464761</v>
+        <v>-0.1554544375558911</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.762179812827506</v>
       </c>
       <c r="E94">
-        <v>-28.29919693427295</v>
+        <v>-29.07607476418483</v>
       </c>
       <c r="F94">
-        <v>-4.452291868098832</v>
+        <v>-5.020787162761688</v>
       </c>
       <c r="G94">
-        <v>-0.1855075699613949</v>
+        <v>-0.4638615494488555</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.361400099800689</v>
       </c>
       <c r="E95">
-        <v>-31.53131827318954</v>
+        <v>-31.65079979564492</v>
       </c>
       <c r="F95">
-        <v>-4.847772690278178</v>
+        <v>-5.511188948893023</v>
       </c>
       <c r="G95">
-        <v>-1.268208246397879</v>
+        <v>-1.607188246346013</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.050165331926839</v>
       </c>
       <c r="E96">
-        <v>-32.37502279403262</v>
+        <v>-33.49567519976278</v>
       </c>
       <c r="F96">
-        <v>-5.120395029478717</v>
+        <v>-5.104912842720394</v>
       </c>
       <c r="G96">
-        <v>-1.401553710174184</v>
+        <v>-1.845908374637319</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.810044774631976</v>
       </c>
       <c r="E97">
-        <v>-35.67012841368489</v>
+        <v>-35.8978495218716</v>
       </c>
       <c r="F97">
-        <v>-5.144235443331286</v>
+        <v>-5.606645038187221</v>
       </c>
       <c r="G97">
-        <v>-1.876981155068919</v>
+        <v>-0.9408052242005769</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.652158002366413</v>
       </c>
       <c r="E98">
-        <v>-37.7742725401639</v>
+        <v>-37.74367137705706</v>
       </c>
       <c r="F98">
-        <v>-5.414102632550115</v>
+        <v>-5.638238142562591</v>
       </c>
       <c r="G98">
-        <v>-2.261213001993351</v>
+        <v>-2.836777828359961</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.526487371346281</v>
       </c>
       <c r="E99">
-        <v>-40.27926586461687</v>
+        <v>-40.561546027648</v>
       </c>
       <c r="F99">
-        <v>-5.42667973482682</v>
+        <v>-5.72476691635682</v>
       </c>
       <c r="G99">
-        <v>-2.677156564638461</v>
+        <v>-2.770106751744578</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.48065510111785</v>
       </c>
       <c r="E100">
-        <v>-42.05848065986051</v>
+        <v>-42.2202377514145</v>
       </c>
       <c r="F100">
-        <v>-5.337834845774365</v>
+        <v>-5.632949016695717</v>
       </c>
       <c r="G100">
-        <v>-3.48320488199467</v>
+        <v>-4.02729304137389</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.40622244389958</v>
       </c>
       <c r="E101">
-        <v>-44.57078746983588</v>
+        <v>-44.59293623620739</v>
       </c>
       <c r="F101">
-        <v>-5.572199864844012</v>
+        <v>-5.679751774953889</v>
       </c>
       <c r="G101">
-        <v>-4.215050631633655</v>
+        <v>-4.269578627210991</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.45044455182749</v>
       </c>
       <c r="E102">
-        <v>-46.86313724031067</v>
+        <v>-46.98712685864069</v>
       </c>
       <c r="F102">
-        <v>-5.575239144844883</v>
+        <v>-5.849306156795905</v>
       </c>
       <c r="G102">
-        <v>-5.06504313047815</v>
+        <v>-5.045590364889393</v>
       </c>
     </row>
   </sheetData>
